--- a/DateBase/orders/Nhat 48_2026-7-28.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-28.xlsx
@@ -773,6 +773,9 @@
       <c r="C41" t="str">
         <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -831,7 +834,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0181010251815162015352025151515141315121510151010510101051055101555515140</v>
+        <v>01810102518151620153520251515151413151215101510105101010510551015555151410</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-28.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-28.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -777,9 +777,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>3</v>
+      </c>
+      <c r="C42" t="str">
+        <v>609_康乃馨小天使_angle_undefined_20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>616_康乃馨紫精灵_Purple Elves_undefined_20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>901_康乃馨新娘_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>619_康乃馨樱桃紫_undefined_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -834,7 +914,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01810102518151620153520251515151413151215101510105101010510551015555151410</v>
+        <v>01810102518151620153520251515151413151215101510105101010510551015555151410551555101010150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-28.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-28.xlsx
@@ -856,6 +856,9 @@
       <c r="C51" t="str">
         <v>619_康乃馨樱桃紫_undefined_undefined_20stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -914,7 +917,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01810102518151620153520251515151413151215101510105101010510551015555151410551555101010150</v>
+        <v>01810102518151620153520251515151413151215101510105101010510551015555151410551555101010151</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-28.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-28.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -857,12 +857,36 @@
         <v>619_康乃馨樱桃紫_undefined_undefined_20stems</v>
       </c>
       <c r="F51" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>789_迷你菊浅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L54"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -917,7 +941,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01810102518151620153520251515151413151215101510105101010510551015555151410551555101010151</v>
+        <v>01810102518151620153520251515151413151215101510105101010510551015555151410551555101010151010510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-28.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-28.xlsx
@@ -943,6 +943,9 @@
       <c r="G2" t="str">
         <v>01810102518151620153520251515151413151215101510105101010510551015555151410551555101010151010510</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
